--- a/Maping/Saksham_Migration_Module_Timeline.xlsx
+++ b/Maping/Saksham_Migration_Module_Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PTFS\Saksham Data Migration eBizWiz to EdifyBiz\Maping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E871908-3A3F-415D-B3A0-B6E429FDD3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656D9396-2B8C-487C-BB81-F0C8C8EBB97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6225" yWindow="1875" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>eBizWiz Menu</t>
   </si>
@@ -58,18 +58,12 @@
     <t>Customer Inquiry</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Quotation Entry</t>
   </si>
   <si>
     <t>Customer Quotation</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>Order Placed</t>
   </si>
   <si>
@@ -179,6 +173,9 @@
   </si>
   <si>
     <t>DMS</t>
+  </si>
+  <si>
+    <t>In Progress / Skeep</t>
   </si>
 </sst>
 </file>
@@ -210,7 +207,7 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,12 +232,6 @@
         <bgColor rgb="FFF6E7D3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7EBEF"/>
-        <bgColor rgb="FFE7EBEF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -254,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -269,7 +260,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,11 +478,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
@@ -557,10 +548,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -572,10 +563,10 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
@@ -587,10 +578,10 @@
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
@@ -602,186 +593,181 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>15</v>
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="D19" s="7">
         <v>46152</v>
       </c>
       <c r="E19" s="3"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="F21" s="6" t="s">
-        <v>12</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
